--- a/education_forms/030_language_immersion_program_registration_form--education_forms.xlsx
+++ b/education_forms/030_language_immersion_program_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'beginner',_'value':_1}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'beginner', 'value': 1}</t>
+          <t>beginner</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'intermediate',_'value':_2}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'intermediate', 'value': 2}</t>
+          <t>intermediate</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'advanced',_'value':_3}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'advanced', 'value': 3}</t>
+          <t>advanced</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_40,_'label':_'english',_'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 40, 'label': 'English', 'value': 'english'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_50,_'label':_'spanish',_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 50, 'label': 'Spanish', 'value': 'spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_60,_'label':_'french',_'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 60, 'label': 'French', 'value': 'french'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_70,_'label':_'3_months',_'value':_3}</t>
+          <t>3_months</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 70, 'label': '3 Months', 'value': 3}</t>
+          <t>3 Months</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_80,_'label':_'6_months',_'value':_6}</t>
+          <t>6_months</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 80, 'label': '6 Months', 'value': 6}</t>
+          <t>6 Months</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_90,_'label':_'12_months',_'value':_12}</t>
+          <t>12_months</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 90, 'label': '12 Months', 'value': 12}</t>
+          <t>12 Months</t>
         </is>
       </c>
     </row>
